--- a/ig/nr-resolve-qa-error/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-resolve-qa-error/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:03:58+00:00</t>
+    <t>2023-12-11T13:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
